--- a/artfynd/A 56248-2023 artfynd.xlsx
+++ b/artfynd/A 56248-2023 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>104346716</v>
       </c>
       <c r="B9" t="n">
-        <v>56872</v>
+        <v>56873</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 56248-2023 artfynd.xlsx
+++ b/artfynd/A 56248-2023 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>104346716</v>
       </c>
       <c r="B9" t="n">
-        <v>56873</v>
+        <v>56876</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 56248-2023 artfynd.xlsx
+++ b/artfynd/A 56248-2023 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>104346716</v>
       </c>
       <c r="B9" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 56248-2023 artfynd.xlsx
+++ b/artfynd/A 56248-2023 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>104346716</v>
       </c>
       <c r="B9" t="n">
-        <v>56880</v>
+        <v>56887</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 56248-2023 artfynd.xlsx
+++ b/artfynd/A 56248-2023 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>104346716</v>
       </c>
       <c r="B9" t="n">
-        <v>56887</v>
+        <v>56889</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 56248-2023 artfynd.xlsx
+++ b/artfynd/A 56248-2023 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>104346716</v>
       </c>
       <c r="B9" t="n">
-        <v>56889</v>
+        <v>56917</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 56248-2023 artfynd.xlsx
+++ b/artfynd/A 56248-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56248-2023 artfynd.xlsx
+++ b/artfynd/A 56248-2023 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1307,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1447,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
